--- a/input/260427-diccionario.xlsx
+++ b/input/260427-diccionario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBEE660-F2DC-E941-9C74-A1BF373CB0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D0B3F6-9191-4943-B095-B21530CCFD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="3800" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4752" uniqueCount="3602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="3603">
   <si>
     <t>tokens</t>
   </si>
@@ -10829,6 +10829,9 @@
   </si>
   <si>
     <t>mov_feminista</t>
+  </si>
+  <si>
+    <t>en_el_fondo</t>
   </si>
 </sst>
 </file>
@@ -11247,7 +11250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3592"/>
+  <dimension ref="A1:M3593"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -11375,6 +11378,9 @@
       <c r="B7">
         <v>9</v>
       </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
       <c r="G7">
         <v>1</v>
       </c>
@@ -11397,6 +11403,9 @@
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
       <c r="G9">
         <v>1</v>
       </c>
@@ -11408,6 +11417,9 @@
       <c r="B10">
         <v>5</v>
       </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
       <c r="G10">
         <v>1</v>
       </c>
@@ -11419,6 +11431,9 @@
       <c r="B11">
         <v>15</v>
       </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -11427,6 +11442,9 @@
       <c r="B12">
         <v>5</v>
       </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
       <c r="G12">
         <v>1</v>
       </c>
@@ -26773,9 +26791,6 @@
       <c r="B1406">
         <v>137</v>
       </c>
-      <c r="C1406" s="3">
-        <v>1</v>
-      </c>
       <c r="E1406">
         <v>1</v>
       </c>
@@ -27791,6 +27806,9 @@
       <c r="E1501">
         <v>1</v>
       </c>
+      <c r="H1501" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="1502" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1502" t="s">
@@ -37553,6 +37571,9 @@
       <c r="G2380">
         <v>1</v>
       </c>
+      <c r="H2380" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="2381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2381" t="s">
@@ -37564,6 +37585,9 @@
       <c r="G2381">
         <v>1</v>
       </c>
+      <c r="H2381" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="2382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2382" t="s">
@@ -37575,6 +37599,9 @@
       <c r="G2382">
         <v>1</v>
       </c>
+      <c r="H2382" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="2383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2383" t="s">
@@ -37583,6 +37610,9 @@
       <c r="B2383">
         <v>10</v>
       </c>
+      <c r="H2383" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="2384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2384" t="s">
@@ -51241,6 +51271,14 @@
       </c>
       <c r="B3592">
         <v>10</v>
+      </c>
+    </row>
+    <row r="3593" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3593" t="s">
+        <v>3602</v>
+      </c>
+      <c r="C3593" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/input/260427-diccionario.xlsx
+++ b/input/260427-diccionario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariana Vallejos\Downloads\Femocratas Final Paper\femocratas-main\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariana Vallejos\Documents\GitHub\femocratas\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142B1879-89F7-4145-AE15-528C95BD7365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F632013-DBCD-46DF-81D0-B30D17DA857D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$3592</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$3592</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -11295,7 +11295,7 @@
         <v>323</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>2361</v>
+        <v>37</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>3601</v>
@@ -11481,7 +11481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -11492,15 +11492,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+      <c r="L18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -11511,7 +11517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -11522,7 +11528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -11544,7 +11550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -11555,7 +11561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -11566,7 +11572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -11580,7 +11586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -11591,7 +11597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -11602,7 +11608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -11610,7 +11616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -11618,7 +11624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -11629,7 +11635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -11643,7 +11649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -11657,7 +11663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -11671,15 +11677,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K34" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -11689,16 +11698,22 @@
       <c r="G35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K35" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K36" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -11708,16 +11723,22 @@
       <c r="G37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K37" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K38" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -11727,8 +11748,11 @@
       <c r="G39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K39" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -11736,7 +11760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -11744,7 +11768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -11758,7 +11782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -11769,7 +11793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -11777,7 +11801,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -11788,7 +11812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -11802,7 +11826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -11813,7 +11837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -11970,7 +11994,7 @@
       <c r="B63">
         <v>38</v>
       </c>
-      <c r="K63" s="11">
+      <c r="L63" s="15">
         <v>1</v>
       </c>
     </row>
@@ -11988,7 +12012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -11998,11 +12022,11 @@
       <c r="G65">
         <v>1</v>
       </c>
-      <c r="K65" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -12012,11 +12036,11 @@
       <c r="G66">
         <v>1</v>
       </c>
-      <c r="K66" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -12027,7 +12051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -12035,7 +12059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -12043,7 +12067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -12051,7 +12075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -12059,7 +12083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -12073,7 +12097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -12087,7 +12111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -12101,7 +12125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -12112,7 +12136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -12120,7 +12144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -12131,7 +12155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -12142,7 +12166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -12150,7 +12174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -12438,6 +12462,9 @@
       <c r="B105">
         <v>10</v>
       </c>
+      <c r="L105" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -12449,6 +12476,9 @@
       <c r="G106">
         <v>1</v>
       </c>
+      <c r="L106" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -12719,7 +12749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>132</v>
       </c>
@@ -12733,7 +12763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>133</v>
       </c>
@@ -12743,8 +12773,11 @@
       <c r="G130">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K130" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -12754,16 +12787,22 @@
       <c r="G131">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K131" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132">
         <v>10</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K132" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>136</v>
       </c>
@@ -12777,7 +12816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>137</v>
       </c>
@@ -12788,7 +12827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -12805,7 +12844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -12816,7 +12855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -12830,7 +12869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>141</v>
       </c>
@@ -12838,7 +12877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>142</v>
       </c>
@@ -12852,7 +12891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -12863,7 +12902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>144</v>
       </c>
@@ -12877,7 +12916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -12888,7 +12927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -12899,7 +12938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -13629,7 +13668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>212</v>
       </c>
@@ -13643,7 +13682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>213</v>
       </c>
@@ -13651,7 +13690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>214</v>
       </c>
@@ -13665,7 +13704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>215</v>
       </c>
@@ -13675,8 +13714,14 @@
       <c r="H212" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L212" s="15">
+        <v>1</v>
+      </c>
+      <c r="M212" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>216</v>
       </c>
@@ -13690,7 +13735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>217</v>
       </c>
@@ -13701,7 +13746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>218</v>
       </c>
@@ -13715,7 +13760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>219</v>
       </c>
@@ -13725,8 +13770,11 @@
       <c r="G216">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K216" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>220</v>
       </c>
@@ -13736,8 +13784,11 @@
       <c r="G217">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K217" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>221</v>
       </c>
@@ -13745,7 +13796,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -13753,7 +13804,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>223</v>
       </c>
@@ -13764,7 +13815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>224</v>
       </c>
@@ -13775,7 +13826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>225</v>
       </c>
@@ -13786,7 +13837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>226</v>
       </c>
@@ -13797,7 +13848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>227</v>
       </c>
@@ -13808,7 +13859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>228</v>
       </c>
@@ -13819,7 +13870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>229</v>
       </c>
@@ -13827,18 +13878,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>230</v>
       </c>
       <c r="B227">
         <v>27</v>
       </c>
-      <c r="K227" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L227" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>231</v>
       </c>
@@ -13849,7 +13900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>232</v>
       </c>
@@ -13860,7 +13911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>233</v>
       </c>
@@ -13871,7 +13922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>234</v>
       </c>
@@ -13882,7 +13933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>235</v>
       </c>
@@ -13893,7 +13944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>236</v>
       </c>
@@ -13907,7 +13958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>237</v>
       </c>
@@ -13921,7 +13972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>238</v>
       </c>
@@ -13935,7 +13986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>239</v>
       </c>
@@ -13949,7 +14000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>240</v>
       </c>
@@ -13960,7 +14011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>241</v>
       </c>
@@ -13974,7 +14025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>242</v>
       </c>
@@ -13985,7 +14036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>243</v>
       </c>
@@ -14530,7 +14581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>292</v>
       </c>
@@ -14541,7 +14592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>293</v>
       </c>
@@ -14552,7 +14603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>294</v>
       </c>
@@ -14566,7 +14617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>295</v>
       </c>
@@ -14580,7 +14631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>296</v>
       </c>
@@ -14588,7 +14639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>297</v>
       </c>
@@ -14599,7 +14650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>298</v>
       </c>
@@ -14607,7 +14658,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>299</v>
       </c>
@@ -14618,7 +14669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>300</v>
       </c>
@@ -14626,7 +14677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>301</v>
       </c>
@@ -14637,7 +14688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>302</v>
       </c>
@@ -14648,7 +14699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>303</v>
       </c>
@@ -14662,7 +14713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>304</v>
       </c>
@@ -14676,7 +14727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>305</v>
       </c>
@@ -14684,15 +14735,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>306</v>
       </c>
       <c r="B303">
         <v>10</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K303" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>307</v>
       </c>
@@ -14732,6 +14786,9 @@
       <c r="G307">
         <v>1</v>
       </c>
+      <c r="K307" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
@@ -14743,6 +14800,9 @@
       <c r="G308">
         <v>1</v>
       </c>
+      <c r="K308" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
@@ -15070,7 +15130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>340</v>
       </c>
@@ -15080,8 +15140,14 @@
       <c r="G337">
         <v>1</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L337" s="15">
+        <v>1</v>
+      </c>
+      <c r="M337" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>341</v>
       </c>
@@ -15092,7 +15158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>342</v>
       </c>
@@ -15103,7 +15169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>343</v>
       </c>
@@ -15114,7 +15180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>344</v>
       </c>
@@ -15125,7 +15191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>345</v>
       </c>
@@ -15136,7 +15202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>346</v>
       </c>
@@ -15147,7 +15213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>347</v>
       </c>
@@ -15155,7 +15221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>348</v>
       </c>
@@ -15163,7 +15229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>349</v>
       </c>
@@ -15171,7 +15237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>350</v>
       </c>
@@ -15179,7 +15245,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>351</v>
       </c>
@@ -15187,7 +15253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>352</v>
       </c>
@@ -15198,7 +15264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>353</v>
       </c>
@@ -15206,7 +15272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>354</v>
       </c>
@@ -15217,7 +15283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>355</v>
       </c>
@@ -15550,7 +15616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>388</v>
       </c>
@@ -15558,7 +15624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>389</v>
       </c>
@@ -15569,7 +15635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>390</v>
       </c>
@@ -15580,7 +15646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>391</v>
       </c>
@@ -15591,7 +15657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>392</v>
       </c>
@@ -15602,7 +15668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>393</v>
       </c>
@@ -15616,7 +15682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>394</v>
       </c>
@@ -15630,7 +15696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>395</v>
       </c>
@@ -15641,7 +15707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>396</v>
       </c>
@@ -15652,7 +15718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>397</v>
       </c>
@@ -15663,7 +15729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>398</v>
       </c>
@@ -15674,7 +15740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>399</v>
       </c>
@@ -15688,7 +15754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>400</v>
       </c>
@@ -15702,7 +15768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>401</v>
       </c>
@@ -15713,7 +15779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>402</v>
       </c>
@@ -15723,8 +15789,11 @@
       <c r="F399">
         <v>1</v>
       </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K399" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>403</v>
       </c>
@@ -15735,7 +15804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>404</v>
       </c>
@@ -15745,16 +15814,22 @@
       <c r="G401">
         <v>1</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K401" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>405</v>
       </c>
       <c r="B402">
         <v>14</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K402" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>406</v>
       </c>
@@ -15765,7 +15840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>407</v>
       </c>
@@ -15776,7 +15851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>408</v>
       </c>
@@ -15784,7 +15859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>409</v>
       </c>
@@ -15795,7 +15870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>410</v>
       </c>
@@ -15806,7 +15881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>411</v>
       </c>
@@ -15817,7 +15892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>412</v>
       </c>
@@ -15828,7 +15903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>413</v>
       </c>
@@ -15839,7 +15914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>414</v>
       </c>
@@ -15850,7 +15925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>415</v>
       </c>
@@ -15864,7 +15939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>416</v>
       </c>
@@ -15878,7 +15953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>417</v>
       </c>
@@ -15889,7 +15964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>418</v>
       </c>
@@ -15903,7 +15978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>419</v>
       </c>
@@ -15917,7 +15992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>420</v>
       </c>
@@ -15931,7 +16006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>421</v>
       </c>
@@ -15945,7 +16020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>422</v>
       </c>
@@ -15955,8 +16030,11 @@
       <c r="G419">
         <v>1</v>
       </c>
-    </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K419" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>423</v>
       </c>
@@ -15966,8 +16044,11 @@
       <c r="G420">
         <v>1</v>
       </c>
-    </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K420" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>424</v>
       </c>
@@ -15975,7 +16056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>425</v>
       </c>
@@ -15983,7 +16064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>426</v>
       </c>
@@ -15994,7 +16075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>427</v>
       </c>
@@ -16008,7 +16089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>428</v>
       </c>
@@ -16022,7 +16103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>429</v>
       </c>
@@ -16033,7 +16114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>430</v>
       </c>
@@ -16041,7 +16122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>431</v>
       </c>
@@ -16055,7 +16136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>432</v>
       </c>
@@ -16069,7 +16150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>433</v>
       </c>
@@ -16083,7 +16164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>434</v>
       </c>
@@ -16094,7 +16175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>435</v>
       </c>
@@ -16145,6 +16226,9 @@
       <c r="G436">
         <v>1</v>
       </c>
+      <c r="K436" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
@@ -16284,7 +16368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>452</v>
       </c>
@@ -16295,7 +16379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>453</v>
       </c>
@@ -16306,7 +16390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>454</v>
       </c>
@@ -16317,7 +16401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>455</v>
       </c>
@@ -16325,7 +16409,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>456</v>
       </c>
@@ -16336,7 +16420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>457</v>
       </c>
@@ -16347,7 +16431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>458</v>
       </c>
@@ -16358,7 +16442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>459</v>
       </c>
@@ -16369,7 +16453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>460</v>
       </c>
@@ -16380,7 +16464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>461</v>
       </c>
@@ -16388,7 +16472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>462</v>
       </c>
@@ -16402,7 +16486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>463</v>
       </c>
@@ -16413,7 +16497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>464</v>
       </c>
@@ -16424,7 +16508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>465</v>
       </c>
@@ -16438,7 +16522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>466</v>
       </c>
@@ -16452,15 +16536,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>467</v>
       </c>
       <c r="B464">
         <v>21</v>
       </c>
-    </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K464" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>468</v>
       </c>
@@ -16470,8 +16557,11 @@
       <c r="G465">
         <v>1</v>
       </c>
-    </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K465" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>469</v>
       </c>
@@ -16481,8 +16571,11 @@
       <c r="G466">
         <v>1</v>
       </c>
-    </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K466" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>470</v>
       </c>
@@ -16490,7 +16583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>471</v>
       </c>
@@ -16500,8 +16593,11 @@
       <c r="G468">
         <v>1</v>
       </c>
-    </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K468" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>472</v>
       </c>
@@ -16511,8 +16607,11 @@
       <c r="G469">
         <v>1</v>
       </c>
-    </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K469" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>473</v>
       </c>
@@ -16526,7 +16625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>474</v>
       </c>
@@ -16537,7 +16636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>475</v>
       </c>
@@ -16548,18 +16647,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>476</v>
       </c>
       <c r="B473">
         <v>14</v>
       </c>
-      <c r="K473" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L473" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>477</v>
       </c>
@@ -16569,11 +16668,11 @@
       <c r="G474">
         <v>1</v>
       </c>
-      <c r="K474" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L474" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>478</v>
       </c>
@@ -16584,7 +16683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>479</v>
       </c>
@@ -16592,7 +16691,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>480</v>
       </c>
@@ -16606,23 +16705,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>481</v>
       </c>
       <c r="B478">
         <v>31</v>
       </c>
-    </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K478" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>482</v>
       </c>
       <c r="B479">
         <v>40</v>
       </c>
-    </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K479" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>483</v>
       </c>
@@ -16802,33 +16907,33 @@
       <c r="B496">
         <v>11</v>
       </c>
-      <c r="K496" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L496" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>500</v>
       </c>
       <c r="B497">
         <v>40</v>
       </c>
-      <c r="K497" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L497" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>501</v>
       </c>
       <c r="B498">
         <v>23</v>
       </c>
-      <c r="K498" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L498" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>502</v>
       </c>
@@ -16842,7 +16947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>503</v>
       </c>
@@ -16853,7 +16958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>504</v>
       </c>
@@ -16861,7 +16966,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>505</v>
       </c>
@@ -16869,7 +16974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>506</v>
       </c>
@@ -16883,7 +16988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>507</v>
       </c>
@@ -16894,7 +16999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>508</v>
       </c>
@@ -16905,7 +17010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>509</v>
       </c>
@@ -16913,7 +17018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>510</v>
       </c>
@@ -16924,7 +17029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>511</v>
       </c>
@@ -16938,7 +17043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>512</v>
       </c>
@@ -16949,7 +17054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>513</v>
       </c>
@@ -16963,7 +17068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>514</v>
       </c>
@@ -16974,7 +17079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>515</v>
       </c>
@@ -16988,7 +17093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>516</v>
       </c>
@@ -17002,7 +17107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>517</v>
       </c>
@@ -17010,7 +17115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>518</v>
       </c>
@@ -17018,7 +17123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>519</v>
       </c>
@@ -17032,7 +17137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>520</v>
       </c>
@@ -17043,7 +17148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>521</v>
       </c>
@@ -17054,7 +17159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>522</v>
       </c>
@@ -17062,7 +17167,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>523</v>
       </c>
@@ -17073,7 +17178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>524</v>
       </c>
@@ -17081,7 +17186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>525</v>
       </c>
@@ -17092,7 +17197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>526</v>
       </c>
@@ -17103,7 +17208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>527</v>
       </c>
@@ -17114,7 +17219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>528</v>
       </c>
@@ -17125,7 +17230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>529</v>
       </c>
@@ -17136,7 +17241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>530</v>
       </c>
@@ -17147,7 +17252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>531</v>
       </c>
@@ -17157,8 +17262,11 @@
       <c r="F528">
         <v>1</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K528" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>532</v>
       </c>
@@ -17168,16 +17276,22 @@
       <c r="E529">
         <v>1</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K529" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>533</v>
       </c>
       <c r="B530">
         <v>34</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K530" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>534</v>
       </c>
@@ -17187,8 +17301,11 @@
       <c r="F531">
         <v>1</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K531" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>535</v>
       </c>
@@ -17196,7 +17313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>536</v>
       </c>
@@ -17204,7 +17321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>537</v>
       </c>
@@ -17215,7 +17332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>538</v>
       </c>
@@ -17226,7 +17343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>539</v>
       </c>
@@ -17234,7 +17351,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>540</v>
       </c>
@@ -17248,7 +17365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>541</v>
       </c>
@@ -17259,7 +17376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>542</v>
       </c>
@@ -17270,7 +17387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>543</v>
       </c>
@@ -17281,7 +17398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>544</v>
       </c>
@@ -17292,7 +17409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>545</v>
       </c>
@@ -17300,7 +17417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>546</v>
       </c>
@@ -17311,7 +17428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>547</v>
       </c>
@@ -17966,7 +18083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>612</v>
       </c>
@@ -17980,7 +18097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>613</v>
       </c>
@@ -17991,7 +18108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>614</v>
       </c>
@@ -18002,15 +18119,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>615</v>
       </c>
       <c r="B612">
         <v>26</v>
       </c>
-    </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K612" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>616</v>
       </c>
@@ -18021,7 +18141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>617</v>
       </c>
@@ -18032,7 +18152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>618</v>
       </c>
@@ -18043,7 +18163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>619</v>
       </c>
@@ -18054,7 +18174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>620</v>
       </c>
@@ -18065,7 +18185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>621</v>
       </c>
@@ -18079,7 +18199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>622</v>
       </c>
@@ -18090,7 +18210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>623</v>
       </c>
@@ -18104,7 +18224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>624</v>
       </c>
@@ -18112,7 +18232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>625</v>
       </c>
@@ -18123,7 +18243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>626</v>
       </c>
@@ -18134,7 +18254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>627</v>
       </c>
@@ -18250,6 +18370,9 @@
       <c r="B635">
         <v>13</v>
       </c>
+      <c r="I635" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
@@ -20066,7 +20189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>805</v>
       </c>
@@ -20077,7 +20200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>806</v>
       </c>
@@ -20088,7 +20211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>807</v>
       </c>
@@ -20096,7 +20219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>808</v>
       </c>
@@ -20104,7 +20227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>809</v>
       </c>
@@ -20112,7 +20235,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>810</v>
       </c>
@@ -20126,7 +20249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>811</v>
       </c>
@@ -20137,7 +20260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>812</v>
       </c>
@@ -20148,7 +20271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>813</v>
       </c>
@@ -20159,7 +20282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>814</v>
       </c>
@@ -20167,7 +20290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>815</v>
       </c>
@@ -20175,7 +20298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>816</v>
       </c>
@@ -20186,7 +20309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>817</v>
       </c>
@@ -20194,7 +20317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>818</v>
       </c>
@@ -20202,7 +20325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>819</v>
       </c>
@@ -20210,7 +20333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>820</v>
       </c>
@@ -20220,16 +20343,22 @@
       <c r="G816">
         <v>1</v>
       </c>
-    </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K816" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>821</v>
       </c>
       <c r="B817">
         <v>16</v>
       </c>
-    </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K817" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>822</v>
       </c>
@@ -20239,8 +20368,11 @@
       <c r="G818">
         <v>1</v>
       </c>
-    </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K818" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>823</v>
       </c>
@@ -20250,16 +20382,22 @@
       <c r="C819" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K819" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>824</v>
       </c>
       <c r="B820">
         <v>19</v>
       </c>
-    </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K820" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>825</v>
       </c>
@@ -20272,8 +20410,11 @@
       <c r="G821">
         <v>1</v>
       </c>
-    </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K821" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="822" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>826</v>
       </c>
@@ -20281,7 +20422,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>827</v>
       </c>
@@ -20289,7 +20430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>828</v>
       </c>
@@ -20300,7 +20441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>829</v>
       </c>
@@ -20308,7 +20449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>830</v>
       </c>
@@ -20319,7 +20460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>831</v>
       </c>
@@ -20330,7 +20471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>832</v>
       </c>
@@ -20344,7 +20485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>833</v>
       </c>
@@ -20355,7 +20496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>834</v>
       </c>
@@ -20366,7 +20507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>835</v>
       </c>
@@ -20377,7 +20518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>836</v>
       </c>
@@ -22020,7 +22161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="977" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>981</v>
       </c>
@@ -22034,7 +22175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="978" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>982</v>
       </c>
@@ -22048,7 +22189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="979" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>983</v>
       </c>
@@ -22062,7 +22203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="980" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>984</v>
       </c>
@@ -22073,7 +22214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="981" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>985</v>
       </c>
@@ -22084,7 +22225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="982" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>986</v>
       </c>
@@ -22098,7 +22239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="983" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>987</v>
       </c>
@@ -22109,7 +22250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="984" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>988</v>
       </c>
@@ -22123,7 +22264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="985" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>989</v>
       </c>
@@ -22134,7 +22275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="986" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>990</v>
       </c>
@@ -22145,7 +22286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="987" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>991</v>
       </c>
@@ -22153,7 +22294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="988" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>992</v>
       </c>
@@ -22164,7 +22305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="989" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>993</v>
       </c>
@@ -22174,8 +22315,11 @@
       <c r="G989">
         <v>1</v>
       </c>
-    </row>
-    <row r="990" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K989" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>994</v>
       </c>
@@ -22185,8 +22329,11 @@
       <c r="G990">
         <v>1</v>
       </c>
-    </row>
-    <row r="991" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K990" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>995</v>
       </c>
@@ -22197,7 +22344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="992" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>996</v>
       </c>
@@ -22882,7 +23029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
         <v>1061</v>
       </c>
@@ -22890,7 +23037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
         <v>1062</v>
       </c>
@@ -22901,7 +23048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
         <v>1063</v>
       </c>
@@ -22911,24 +23058,33 @@
       <c r="G1059">
         <v>1</v>
       </c>
-    </row>
-    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1059" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
         <v>1064</v>
       </c>
       <c r="B1060">
         <v>19</v>
       </c>
-    </row>
-    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1060" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
         <v>1065</v>
       </c>
       <c r="B1061">
         <v>19</v>
       </c>
-    </row>
-    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1061" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
         <v>1066</v>
       </c>
@@ -22939,7 +23095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
         <v>1067</v>
       </c>
@@ -22947,23 +23103,29 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
         <v>1068</v>
       </c>
       <c r="B1064">
         <v>19</v>
       </c>
-    </row>
-    <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1064" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
         <v>1069</v>
       </c>
       <c r="B1065">
         <v>15</v>
       </c>
-    </row>
-    <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1065" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
         <v>1070</v>
       </c>
@@ -22971,7 +23133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1067" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
         <v>1071</v>
       </c>
@@ -22979,7 +23141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
         <v>1072</v>
       </c>
@@ -22990,7 +23152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
         <v>1073</v>
       </c>
@@ -23001,7 +23163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
         <v>1074</v>
       </c>
@@ -23012,7 +23174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
         <v>1075</v>
       </c>
@@ -23026,7 +23188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
         <v>1076</v>
       </c>
@@ -24117,7 +24279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
         <v>1173</v>
       </c>
@@ -24128,7 +24290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1170" t="s">
         <v>1174</v>
       </c>
@@ -24142,7 +24304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1171" t="s">
         <v>1175</v>
       </c>
@@ -24153,7 +24315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1172" t="s">
         <v>1176</v>
       </c>
@@ -24164,7 +24326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1173" t="s">
         <v>1177</v>
       </c>
@@ -24178,7 +24340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1174" t="s">
         <v>1178</v>
       </c>
@@ -24189,7 +24351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1175" t="s">
         <v>1179</v>
       </c>
@@ -24200,7 +24362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1176" t="s">
         <v>1180</v>
       </c>
@@ -24214,7 +24376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1177" t="s">
         <v>1181</v>
       </c>
@@ -24227,8 +24389,11 @@
       <c r="G1177">
         <v>1</v>
       </c>
-    </row>
-    <row r="1178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1177" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1178" t="s">
         <v>1182</v>
       </c>
@@ -24242,7 +24407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1179" t="s">
         <v>1183</v>
       </c>
@@ -24253,7 +24418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1180" t="s">
         <v>1184</v>
       </c>
@@ -24267,7 +24432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1181" t="s">
         <v>1185</v>
       </c>
@@ -24281,7 +24446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
         <v>1186</v>
       </c>
@@ -24295,7 +24460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1183" t="s">
         <v>1187</v>
       </c>
@@ -24306,7 +24471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1184" t="s">
         <v>1188</v>
       </c>
@@ -25391,7 +25556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
         <v>1285</v>
       </c>
@@ -25405,7 +25570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1282" t="s">
         <v>1286</v>
       </c>
@@ -25419,7 +25584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1283" t="s">
         <v>1287</v>
       </c>
@@ -25433,7 +25598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1284" t="s">
         <v>1288</v>
       </c>
@@ -25444,7 +25609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1285" t="s">
         <v>1289</v>
       </c>
@@ -25452,7 +25617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1286" t="s">
         <v>1290</v>
       </c>
@@ -25463,7 +25628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1287" t="s">
         <v>1291</v>
       </c>
@@ -25471,7 +25636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1288" t="s">
         <v>1292</v>
       </c>
@@ -25482,7 +25647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1289" t="s">
         <v>1293</v>
       </c>
@@ -25495,8 +25660,11 @@
       <c r="G1289">
         <v>1</v>
       </c>
-    </row>
-    <row r="1290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1289" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1290" t="s">
         <v>1294</v>
       </c>
@@ -25510,7 +25678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1291" t="s">
         <v>1295</v>
       </c>
@@ -25520,8 +25688,11 @@
       <c r="C1291" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="1292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1291" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1292" t="s">
         <v>1296</v>
       </c>
@@ -25531,24 +25702,33 @@
       <c r="G1292">
         <v>1</v>
       </c>
-    </row>
-    <row r="1293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1292" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1293" t="s">
         <v>1297</v>
       </c>
       <c r="B1293">
         <v>27</v>
       </c>
-    </row>
-    <row r="1294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1293" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1294" t="s">
         <v>1298</v>
       </c>
       <c r="B1294">
         <v>14</v>
       </c>
-    </row>
-    <row r="1295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1294" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1295" t="s">
         <v>1299</v>
       </c>
@@ -25558,8 +25738,11 @@
       <c r="G1295">
         <v>1</v>
       </c>
-    </row>
-    <row r="1296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1295" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1296" t="s">
         <v>1300</v>
       </c>
@@ -25567,7 +25750,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="1297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1297" t="s">
         <v>1301</v>
       </c>
@@ -25575,7 +25758,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="1298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1298" t="s">
         <v>1302</v>
       </c>
@@ -25583,15 +25766,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1299" t="s">
         <v>1303</v>
       </c>
       <c r="B1299">
         <v>14</v>
       </c>
-    </row>
-    <row r="1300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1299" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1300" t="s">
         <v>1304</v>
       </c>
@@ -25599,7 +25785,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1301" t="s">
         <v>1305</v>
       </c>
@@ -25610,7 +25796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1302" t="s">
         <v>1306</v>
       </c>
@@ -25621,7 +25807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1303" t="s">
         <v>1307</v>
       </c>
@@ -25629,7 +25815,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1304" t="s">
         <v>1308</v>
       </c>
@@ -25643,7 +25829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1305" t="s">
         <v>1309</v>
       </c>
@@ -25657,7 +25843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1306" t="s">
         <v>1310</v>
       </c>
@@ -25668,7 +25854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1307" t="s">
         <v>1311</v>
       </c>
@@ -25679,7 +25865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1308" t="s">
         <v>1312</v>
       </c>
@@ -25687,7 +25873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1309" t="s">
         <v>1313</v>
       </c>
@@ -25695,7 +25881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1310" t="s">
         <v>1314</v>
       </c>
@@ -25709,7 +25895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1311" t="s">
         <v>1315</v>
       </c>
@@ -25717,7 +25903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1312" t="s">
         <v>1316</v>
       </c>
@@ -27276,18 +27462,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1457" t="s">
         <v>1461</v>
       </c>
       <c r="B1457">
         <v>14</v>
       </c>
-      <c r="K1457" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1458" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1457" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1458" t="s">
         <v>1462</v>
       </c>
@@ -27298,7 +27484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1459" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1459" t="s">
         <v>1463</v>
       </c>
@@ -27309,7 +27495,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1460" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1460" t="s">
         <v>1464</v>
       </c>
@@ -27317,7 +27503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1461" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1461" t="s">
         <v>1465</v>
       </c>
@@ -27325,7 +27511,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="1462" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1462" t="s">
         <v>1466</v>
       </c>
@@ -27336,7 +27522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1463" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1463" t="s">
         <v>1467</v>
       </c>
@@ -27344,7 +27530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1464" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1464" t="s">
         <v>1468</v>
       </c>
@@ -27355,7 +27541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1465" t="s">
         <v>1469</v>
       </c>
@@ -27363,7 +27549,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="1466" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1466" t="s">
         <v>1470</v>
       </c>
@@ -27374,7 +27560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1467" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1467" t="s">
         <v>1471</v>
       </c>
@@ -27388,7 +27574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1468" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1468" t="s">
         <v>1472</v>
       </c>
@@ -27399,7 +27585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1469" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1469" t="s">
         <v>1473</v>
       </c>
@@ -27413,7 +27599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1470" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1470" t="s">
         <v>1474</v>
       </c>
@@ -27427,7 +27613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1471" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1471" t="s">
         <v>1475</v>
       </c>
@@ -27441,7 +27627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1472" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1472" t="s">
         <v>1476</v>
       </c>
@@ -30456,7 +30642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1745" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1745" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1745" t="s">
         <v>1749</v>
       </c>
@@ -30467,7 +30653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1746" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1746" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1746" t="s">
         <v>1750</v>
       </c>
@@ -30475,7 +30661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1747" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1747" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1747" t="s">
         <v>1751</v>
       </c>
@@ -30486,7 +30672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1748" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1748" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1748" t="s">
         <v>1752</v>
       </c>
@@ -30497,7 +30683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1749" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1749" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1749" t="s">
         <v>1753</v>
       </c>
@@ -30505,7 +30691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1750" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1750" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1750" t="s">
         <v>1754</v>
       </c>
@@ -30513,7 +30699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1751" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1751" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1751" t="s">
         <v>1755</v>
       </c>
@@ -30524,15 +30710,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1752" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1752" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1752" t="s">
         <v>1756</v>
       </c>
       <c r="B1752">
         <v>10</v>
       </c>
-    </row>
-    <row r="1753" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1752" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1753" t="s">
         <v>1757</v>
       </c>
@@ -30543,7 +30732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1754" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1754" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1754" t="s">
         <v>1758</v>
       </c>
@@ -30554,7 +30743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1755" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1755" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1755" t="s">
         <v>1759</v>
       </c>
@@ -30562,7 +30751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1756" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1756" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1756" t="s">
         <v>1760</v>
       </c>
@@ -30573,7 +30762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1757" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1757" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1757" t="s">
         <v>1761</v>
       </c>
@@ -30587,7 +30776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1758" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1758" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1758" t="s">
         <v>1762</v>
       </c>
@@ -30598,7 +30787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1759" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1759" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1759" t="s">
         <v>1763</v>
       </c>
@@ -30609,7 +30798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1760" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1760" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1760" t="s">
         <v>1764</v>
       </c>
@@ -30623,7 +30812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1761" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1761" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1761" t="s">
         <v>1765</v>
       </c>
@@ -30634,7 +30823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1762" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1762" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1762" t="s">
         <v>1766</v>
       </c>
@@ -30644,8 +30833,11 @@
       <c r="G1762">
         <v>1</v>
       </c>
-    </row>
-    <row r="1763" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1762" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1763" t="s">
         <v>1767</v>
       </c>
@@ -30655,8 +30847,11 @@
       <c r="G1763">
         <v>1</v>
       </c>
-    </row>
-    <row r="1764" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1763" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1764" t="s">
         <v>1768</v>
       </c>
@@ -30667,7 +30862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1765" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1765" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1765" t="s">
         <v>1769</v>
       </c>
@@ -30678,7 +30873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1766" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1766" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1766" t="s">
         <v>1770</v>
       </c>
@@ -30692,7 +30887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1767" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1767" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1767" t="s">
         <v>1771</v>
       </c>
@@ -30700,7 +30895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1768" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1768" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1768" t="s">
         <v>1772</v>
       </c>
@@ -30711,7 +30906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1769" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1769" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1769" t="s">
         <v>1773</v>
       </c>
@@ -30719,7 +30914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="1770" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1770" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1770" t="s">
         <v>1774</v>
       </c>
@@ -30730,7 +30925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1771" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1771" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1771" t="s">
         <v>1775</v>
       </c>
@@ -30738,7 +30933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="1772" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1772" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1772" t="s">
         <v>1776</v>
       </c>
@@ -30749,7 +30944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1773" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1773" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1773" t="s">
         <v>1777</v>
       </c>
@@ -30757,7 +30952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="1774" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1774" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1774" t="s">
         <v>1778</v>
       </c>
@@ -30768,7 +30963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1775" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1775" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1775" t="s">
         <v>1779</v>
       </c>
@@ -30776,7 +30971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1776" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1776" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1776" t="s">
         <v>1780</v>
       </c>
@@ -30787,7 +30982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1777" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1777" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1777" t="s">
         <v>1781</v>
       </c>
@@ -30798,7 +30993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1778" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1778" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1778" t="s">
         <v>1782</v>
       </c>
@@ -30806,7 +31001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1779" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1779" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1779" t="s">
         <v>1783</v>
       </c>
@@ -30814,7 +31009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1780" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1780" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1780" t="s">
         <v>1784</v>
       </c>
@@ -30825,7 +31020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1781" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1781" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1781" t="s">
         <v>1785</v>
       </c>
@@ -30836,7 +31031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1782" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1782" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1782" t="s">
         <v>1786</v>
       </c>
@@ -30846,8 +31041,11 @@
       <c r="G1782">
         <v>1</v>
       </c>
-    </row>
-    <row r="1783" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1782" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1783" t="s">
         <v>1787</v>
       </c>
@@ -30857,16 +31055,22 @@
       <c r="F1783">
         <v>1</v>
       </c>
-    </row>
-    <row r="1784" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1783" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1784" t="s">
         <v>1788</v>
       </c>
       <c r="B1784">
         <v>11</v>
       </c>
-    </row>
-    <row r="1785" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1784" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1785" t="s">
         <v>1789</v>
       </c>
@@ -30876,8 +31080,11 @@
       <c r="G1785">
         <v>1</v>
       </c>
-    </row>
-    <row r="1786" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1785" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1786" t="s">
         <v>1790</v>
       </c>
@@ -30887,8 +31094,11 @@
       <c r="G1786">
         <v>1</v>
       </c>
-    </row>
-    <row r="1787" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K1786" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1787" t="s">
         <v>1791</v>
       </c>
@@ -30899,7 +31109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1788" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1788" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1788" t="s">
         <v>1792</v>
       </c>
@@ -30910,7 +31120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1789" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1789" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1789" t="s">
         <v>1793</v>
       </c>
@@ -30921,7 +31131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1790" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1790" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1790" t="s">
         <v>1794</v>
       </c>
@@ -30932,7 +31142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1791" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1791" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1791" t="s">
         <v>1795</v>
       </c>
@@ -30943,7 +31153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1792" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1792" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1792" t="s">
         <v>1796</v>
       </c>
@@ -30954,7 +31164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1793" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1793" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1793" t="s">
         <v>1797</v>
       </c>
@@ -30965,7 +31175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1794" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1794" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1794" t="s">
         <v>1798</v>
       </c>
@@ -30976,7 +31186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1795" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1795" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1795" t="s">
         <v>1799</v>
       </c>
@@ -30986,16 +31196,22 @@
       <c r="F1795">
         <v>1</v>
       </c>
-    </row>
-    <row r="1796" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M1795" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1796" t="s">
         <v>1800</v>
       </c>
       <c r="B1796">
         <v>21</v>
       </c>
-    </row>
-    <row r="1797" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M1796" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1797" t="s">
         <v>1801</v>
       </c>
@@ -31003,7 +31219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1798" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1798" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1798" t="s">
         <v>1802</v>
       </c>
@@ -31011,7 +31227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1799" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1799" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1799" t="s">
         <v>1803</v>
       </c>
@@ -31022,7 +31238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1800" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1800" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1800" t="s">
         <v>1804</v>
       </c>
@@ -31033,7 +31249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1801" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1801" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1801" t="s">
         <v>1805</v>
       </c>
@@ -31044,7 +31260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1802" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1802" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1802" t="s">
         <v>1806</v>
       </c>
@@ -31052,7 +31268,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="1803" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1803" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1803" t="s">
         <v>1807</v>
       </c>
@@ -31063,7 +31279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1804" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1804" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1804" t="s">
         <v>1808</v>
       </c>
@@ -31071,7 +31287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1805" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1805" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1805" t="s">
         <v>1809</v>
       </c>
@@ -31079,7 +31295,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1806" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1806" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1806" t="s">
         <v>1810</v>
       </c>
@@ -31090,7 +31306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1807" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1807" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1807" t="s">
         <v>1811</v>
       </c>
@@ -31098,7 +31314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1808" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1808" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1808" t="s">
         <v>1812</v>
       </c>
@@ -33266,7 +33482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2001" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2001" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2001" t="s">
         <v>2005</v>
       </c>
@@ -33277,7 +33493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2002" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2002" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2002" t="s">
         <v>2006</v>
       </c>
@@ -33288,7 +33504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2003" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2003" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2003" t="s">
         <v>2007</v>
       </c>
@@ -33302,7 +33518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2004" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2004" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2004" t="s">
         <v>2008</v>
       </c>
@@ -33313,7 +33529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2005" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2005" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2005" t="s">
         <v>2009</v>
       </c>
@@ -33321,7 +33537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2006" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2006" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2006" t="s">
         <v>2010</v>
       </c>
@@ -33332,7 +33548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2007" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2007" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2007" t="s">
         <v>2011</v>
       </c>
@@ -33342,24 +33558,33 @@
       <c r="G2007">
         <v>1</v>
       </c>
-    </row>
-    <row r="2008" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2007" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2008" t="s">
         <v>2012</v>
       </c>
       <c r="B2008">
         <v>23</v>
       </c>
-    </row>
-    <row r="2009" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2008" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2009" t="s">
         <v>2013</v>
       </c>
       <c r="B2009">
         <v>16</v>
       </c>
-    </row>
-    <row r="2010" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2009" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2010" t="s">
         <v>2014</v>
       </c>
@@ -33369,8 +33594,11 @@
       <c r="G2010">
         <v>1</v>
       </c>
-    </row>
-    <row r="2011" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K2010" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2011" t="s">
         <v>2015</v>
       </c>
@@ -33381,7 +33609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2012" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2012" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2012" t="s">
         <v>2016</v>
       </c>
@@ -33392,7 +33620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2013" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2013" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2013" t="s">
         <v>2017</v>
       </c>
@@ -33406,7 +33634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2014" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2014" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2014" t="s">
         <v>2018</v>
       </c>
@@ -33417,7 +33645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2015" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2015" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2015" t="s">
         <v>2019</v>
       </c>
@@ -33428,7 +33656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2016" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2016" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2016" t="s">
         <v>2020</v>
       </c>
@@ -33821,7 +34049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2049" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2049" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2049" t="s">
         <v>2053</v>
       </c>
@@ -33832,7 +34060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2050" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2050" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2050" t="s">
         <v>2054</v>
       </c>
@@ -33843,7 +34071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2051" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2051" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2051" t="s">
         <v>2055</v>
       </c>
@@ -33854,18 +34082,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2052" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2052" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2052" t="s">
         <v>2056</v>
       </c>
       <c r="B2052">
         <v>15</v>
       </c>
+      <c r="C2052" s="3">
+        <v>1</v>
+      </c>
       <c r="D2052">
         <v>1</v>
       </c>
     </row>
-    <row r="2053" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2053" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2053" t="s">
         <v>2057</v>
       </c>
@@ -33879,7 +34110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2054" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2054" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2054" t="s">
         <v>2058</v>
       </c>
@@ -33890,7 +34121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2055" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2055" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2055" t="s">
         <v>2059</v>
       </c>
@@ -33904,7 +34135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2056" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2056" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2056" t="s">
         <v>2060</v>
       </c>
@@ -33918,7 +34149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2057" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2057" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2057" t="s">
         <v>2061</v>
       </c>
@@ -33932,7 +34163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2058" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2058" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2058" t="s">
         <v>2062</v>
       </c>
@@ -33946,7 +34177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2059" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2059" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2059" t="s">
         <v>2063</v>
       </c>
@@ -33957,7 +34188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2060" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2060" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2060" t="s">
         <v>2064</v>
       </c>
@@ -33971,7 +34202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2061" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2061" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2061" t="s">
         <v>2065</v>
       </c>
@@ -33985,7 +34216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2062" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2062" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2062" t="s">
         <v>2066</v>
       </c>
@@ -33995,8 +34226,11 @@
       <c r="C2062" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2063" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2062" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2063" t="s">
         <v>2067</v>
       </c>
@@ -34007,7 +34241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2064" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2064" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2064" t="s">
         <v>2068</v>
       </c>
@@ -34015,6 +34249,9 @@
         <v>56</v>
       </c>
       <c r="F2064">
+        <v>1</v>
+      </c>
+      <c r="K2064" s="11">
         <v>1</v>
       </c>
     </row>
@@ -34028,6 +34265,9 @@
       <c r="G2065">
         <v>1</v>
       </c>
+      <c r="K2065" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="2066" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2066" t="s">
@@ -34319,7 +34559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2097" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2097" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2097" t="s">
         <v>2101</v>
       </c>
@@ -34330,7 +34570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2098" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2098" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2098" t="s">
         <v>2102</v>
       </c>
@@ -34344,7 +34584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2099" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2099" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2099" t="s">
         <v>2103</v>
       </c>
@@ -34358,7 +34598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2100" t="s">
         <v>2104</v>
       </c>
@@ -34369,7 +34609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2101" t="s">
         <v>2105</v>
       </c>
@@ -34377,7 +34617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2102" t="s">
         <v>2106</v>
       </c>
@@ -34385,7 +34625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2103" t="s">
         <v>2107</v>
       </c>
@@ -34396,7 +34636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2104" t="s">
         <v>2108</v>
       </c>
@@ -34407,7 +34647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2105" t="s">
         <v>2109</v>
       </c>
@@ -34415,7 +34655,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2106" t="s">
         <v>2110</v>
       </c>
@@ -34423,7 +34663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2107" t="s">
         <v>2111</v>
       </c>
@@ -34437,7 +34677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2108" t="s">
         <v>2112</v>
       </c>
@@ -34448,7 +34688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2109" t="s">
         <v>2113</v>
       </c>
@@ -34459,7 +34699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2110" t="s">
         <v>2114</v>
       </c>
@@ -34473,7 +34713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2111" t="s">
         <v>2115</v>
       </c>
@@ -34483,8 +34723,11 @@
       <c r="G2111">
         <v>1</v>
       </c>
-    </row>
-    <row r="2112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K2111" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2112" t="s">
         <v>2116</v>
       </c>
@@ -34492,6 +34735,9 @@
         <v>5</v>
       </c>
       <c r="G2112">
+        <v>1</v>
+      </c>
+      <c r="K2112" s="11">
         <v>1</v>
       </c>
     </row>
@@ -34505,6 +34751,9 @@
       <c r="G2113">
         <v>1</v>
       </c>
+      <c r="K2113" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="2114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2114" t="s">
@@ -35571,6 +35820,9 @@
       <c r="G2202">
         <v>1</v>
       </c>
+      <c r="K2202" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="2203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2203" t="s">
@@ -35612,9 +35864,6 @@
       <c r="B2206">
         <v>27</v>
       </c>
-      <c r="K2206" s="11">
-        <v>1</v>
-      </c>
       <c r="L2206" s="15">
         <v>1</v>
       </c>
@@ -37270,7 +37519,7 @@
       <c r="D2357">
         <v>1</v>
       </c>
-      <c r="K2357" s="11">
+      <c r="L2357" s="15">
         <v>1</v>
       </c>
     </row>
@@ -37287,9 +37536,6 @@
       <c r="G2358">
         <v>1</v>
       </c>
-      <c r="K2358" s="11">
-        <v>1</v>
-      </c>
     </row>
     <row r="2359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2359" t="s">
@@ -37392,7 +37638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2369" t="s">
         <v>2373</v>
       </c>
@@ -37403,7 +37649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2370" t="s">
         <v>2374</v>
       </c>
@@ -37414,7 +37660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2371" t="s">
         <v>2375</v>
       </c>
@@ -37422,18 +37668,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2372" t="s">
         <v>2376</v>
       </c>
       <c r="B2372">
         <v>34</v>
       </c>
-      <c r="K2372" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2373" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2372" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2373" t="s">
         <v>2377</v>
       </c>
@@ -37443,11 +37689,8 @@
       <c r="G2373">
         <v>1</v>
       </c>
-      <c r="K2373" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2374" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2374" t="s">
         <v>2378</v>
       </c>
@@ -37457,11 +37700,8 @@
       <c r="F2374">
         <v>1</v>
       </c>
-      <c r="K2374" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2375" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2375" t="s">
         <v>2379</v>
       </c>
@@ -37471,11 +37711,8 @@
       <c r="G2375">
         <v>1</v>
       </c>
-      <c r="K2375" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2376" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2376" t="s">
         <v>2380</v>
       </c>
@@ -37485,11 +37722,11 @@
       <c r="G2376">
         <v>1</v>
       </c>
-      <c r="K2376" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2377" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2376" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2377" t="s">
         <v>2381</v>
       </c>
@@ -37499,22 +37736,22 @@
       <c r="F2377">
         <v>1</v>
       </c>
-      <c r="K2377" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2378" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2377" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2378" t="s">
         <v>2382</v>
       </c>
       <c r="B2378">
         <v>17</v>
       </c>
-      <c r="K2378" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2379" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2378" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2379" t="s">
         <v>2383</v>
       </c>
@@ -37524,11 +37761,11 @@
       <c r="F2379">
         <v>1</v>
       </c>
-      <c r="K2379" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2380" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2379" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2380" t="s">
         <v>2384</v>
       </c>
@@ -37539,7 +37776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2381" t="s">
         <v>2385</v>
       </c>
@@ -37550,7 +37787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2382" t="s">
         <v>2386</v>
       </c>
@@ -37561,7 +37798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2383" t="s">
         <v>2387</v>
       </c>
@@ -37569,7 +37806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2384" t="s">
         <v>2388</v>
       </c>
@@ -40698,7 +40935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2657" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2657" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2657" t="s">
         <v>2661</v>
       </c>
@@ -40708,8 +40945,11 @@
       <c r="G2657">
         <v>1</v>
       </c>
-    </row>
-    <row r="2658" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K2657" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2658" t="s">
         <v>2662</v>
       </c>
@@ -40723,7 +40963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2659" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2659" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2659" t="s">
         <v>2663</v>
       </c>
@@ -40734,7 +40974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2660" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2660" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2660" t="s">
         <v>2664</v>
       </c>
@@ -40748,7 +40988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2661" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2661" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2661" t="s">
         <v>2665</v>
       </c>
@@ -40762,7 +41002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2662" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2662" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2662" t="s">
         <v>2666</v>
       </c>
@@ -40773,7 +41013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2663" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2663" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2663" t="s">
         <v>2667</v>
       </c>
@@ -40781,7 +41021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2664" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2664" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2664" t="s">
         <v>2668</v>
       </c>
@@ -40792,7 +41032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2665" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2665" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2665" t="s">
         <v>2669</v>
       </c>
@@ -40800,7 +41040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2666" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2666" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2666" t="s">
         <v>2670</v>
       </c>
@@ -40811,7 +41051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2667" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2667" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2667" t="s">
         <v>2671</v>
       </c>
@@ -40819,7 +41059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2668" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2668" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2668" t="s">
         <v>2672</v>
       </c>
@@ -40833,7 +41073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2669" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2669" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2669" t="s">
         <v>2673</v>
       </c>
@@ -40847,7 +41087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2670" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2670" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2670" t="s">
         <v>2674</v>
       </c>
@@ -40855,7 +41095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2671" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2671" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2671" t="s">
         <v>2675</v>
       </c>
@@ -40866,7 +41106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2672" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2672" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2672" t="s">
         <v>2676</v>
       </c>
@@ -41587,7 +41827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2737" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2737" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2737" t="s">
         <v>2741</v>
       </c>
@@ -41598,7 +41838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2738" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2738" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2738" t="s">
         <v>2742</v>
       </c>
@@ -41609,7 +41849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2739" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2739" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2739" t="s">
         <v>2743</v>
       </c>
@@ -41620,7 +41860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2740" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2740" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2740" t="s">
         <v>2744</v>
       </c>
@@ -41631,7 +41871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2741" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2741" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2741" t="s">
         <v>2745</v>
       </c>
@@ -41639,7 +41879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2742" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2742" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2742" t="s">
         <v>2746</v>
       </c>
@@ -41650,7 +41890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2743" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2743" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2743" t="s">
         <v>2747</v>
       </c>
@@ -41661,7 +41901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2744" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2744" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2744" t="s">
         <v>2748</v>
       </c>
@@ -41672,7 +41912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2745" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2745" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2745" t="s">
         <v>2749</v>
       </c>
@@ -41683,7 +41923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2746" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2746" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2746" t="s">
         <v>2750</v>
       </c>
@@ -41694,7 +41934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2747" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2747" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2747" t="s">
         <v>2751</v>
       </c>
@@ -41702,7 +41942,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2748" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2748" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2748" t="s">
         <v>2752</v>
       </c>
@@ -41713,7 +41953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2749" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2749" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2749" t="s">
         <v>2753</v>
       </c>
@@ -41724,7 +41964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2750" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2750" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2750" t="s">
         <v>2754</v>
       </c>
@@ -41735,7 +41975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2751" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2751" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2751" t="s">
         <v>2755</v>
       </c>
@@ -41745,16 +41985,22 @@
       <c r="G2751">
         <v>1</v>
       </c>
-    </row>
-    <row r="2752" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K2751" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2752" t="s">
         <v>2756</v>
       </c>
       <c r="B2752">
         <v>16</v>
       </c>
-    </row>
-    <row r="2753" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K2752" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2753" t="s">
         <v>2757</v>
       </c>
@@ -41764,16 +42010,22 @@
       <c r="G2753">
         <v>1</v>
       </c>
-    </row>
-    <row r="2754" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K2753" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2754" t="s">
         <v>2758</v>
       </c>
       <c r="B2754">
         <v>12</v>
       </c>
-    </row>
-    <row r="2755" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K2754" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2755" t="s">
         <v>2759</v>
       </c>
@@ -41787,7 +42039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2756" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2756" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2756" t="s">
         <v>2760</v>
       </c>
@@ -41801,7 +42053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2757" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2757" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2757" t="s">
         <v>2761</v>
       </c>
@@ -41815,7 +42067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2758" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2758" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2758" t="s">
         <v>2762</v>
       </c>
@@ -41829,7 +42081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2759" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2759" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2759" t="s">
         <v>2763</v>
       </c>
@@ -41843,7 +42095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2760" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2760" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2760" t="s">
         <v>2764</v>
       </c>
@@ -41851,7 +42103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2761" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2761" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2761" t="s">
         <v>2765</v>
       </c>
@@ -41859,7 +42111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2762" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2762" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2762" t="s">
         <v>2766</v>
       </c>
@@ -41873,7 +42125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2763" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2763" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2763" t="s">
         <v>2767</v>
       </c>
@@ -41884,7 +42136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2764" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2764" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2764" t="s">
         <v>2768</v>
       </c>
@@ -41898,7 +42150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2765" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2765" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2765" t="s">
         <v>2769</v>
       </c>
@@ -41909,7 +42161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2766" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2766" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2766" t="s">
         <v>2770</v>
       </c>
@@ -41920,7 +42172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2767" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2767" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2767" t="s">
         <v>2771</v>
       </c>
@@ -41931,7 +42183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2768" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2768" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2768" t="s">
         <v>2772</v>
       </c>
@@ -43294,6 +43546,9 @@
       <c r="G2885">
         <v>1</v>
       </c>
+      <c r="K2885" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="2886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2886" t="s">
@@ -46128,7 +46383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3137" t="s">
         <v>3141</v>
       </c>
@@ -46136,7 +46391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3138" t="s">
         <v>3142</v>
       </c>
@@ -46150,7 +46405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3139" t="s">
         <v>3143</v>
       </c>
@@ -46164,7 +46419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3140" t="s">
         <v>3144</v>
       </c>
@@ -46178,7 +46433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3141" t="s">
         <v>3145</v>
       </c>
@@ -46189,7 +46444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3142" t="s">
         <v>3146</v>
       </c>
@@ -46197,7 +46452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3143" t="s">
         <v>3147</v>
       </c>
@@ -46211,7 +46466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3144" t="s">
         <v>3148</v>
       </c>
@@ -46219,7 +46474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3145" t="s">
         <v>3149</v>
       </c>
@@ -46227,7 +46482,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3146" t="s">
         <v>3150</v>
       </c>
@@ -46235,7 +46490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3147" t="s">
         <v>3151</v>
       </c>
@@ -46243,7 +46498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3148" t="s">
         <v>3152</v>
       </c>
@@ -46253,8 +46508,11 @@
       <c r="G3148">
         <v>1</v>
       </c>
-    </row>
-    <row r="3149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3148" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3149" t="s">
         <v>3153</v>
       </c>
@@ -46264,8 +46522,11 @@
       <c r="G3149">
         <v>1</v>
       </c>
-    </row>
-    <row r="3150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3149" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3150" t="s">
         <v>3154</v>
       </c>
@@ -46275,8 +46536,11 @@
       <c r="G3150">
         <v>1</v>
       </c>
-    </row>
-    <row r="3151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3150" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3151" t="s">
         <v>3155</v>
       </c>
@@ -46287,7 +46551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3152" t="s">
         <v>3156</v>
       </c>
@@ -46852,7 +47116,7 @@
       <c r="B3200">
         <v>16</v>
       </c>
-      <c r="K3200" s="11">
+      <c r="L3200" s="15">
         <v>1</v>
       </c>
     </row>
@@ -46863,6 +47127,9 @@
       <c r="B3201">
         <v>20</v>
       </c>
+      <c r="K3201" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="3202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3202" t="s">
@@ -46874,6 +47141,9 @@
       <c r="G3202">
         <v>1</v>
       </c>
+      <c r="K3202" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="3203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3203" t="s">
@@ -47751,7 +48021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3281" t="s">
         <v>3285</v>
       </c>
@@ -47759,7 +48029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3282" t="s">
         <v>3286</v>
       </c>
@@ -47773,7 +48043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3283" t="s">
         <v>3287</v>
       </c>
@@ -47781,7 +48051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3284" t="s">
         <v>3288</v>
       </c>
@@ -47791,8 +48061,11 @@
       <c r="G3284">
         <v>1</v>
       </c>
-    </row>
-    <row r="3285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3284" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3285" t="s">
         <v>3289</v>
       </c>
@@ -47803,7 +48076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3286" t="s">
         <v>3290</v>
       </c>
@@ -47814,7 +48087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3287" t="s">
         <v>3291</v>
       </c>
@@ -47825,7 +48098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3288" t="s">
         <v>3292</v>
       </c>
@@ -47839,7 +48112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3289" t="s">
         <v>3293</v>
       </c>
@@ -47853,7 +48126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3290" t="s">
         <v>3294</v>
       </c>
@@ -47867,7 +48140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3291" t="s">
         <v>3295</v>
       </c>
@@ -47878,7 +48151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3292" t="s">
         <v>3296</v>
       </c>
@@ -47889,7 +48162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3293" t="s">
         <v>3297</v>
       </c>
@@ -47903,7 +48176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3294" t="s">
         <v>3298</v>
       </c>
@@ -47917,7 +48190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3295" t="s">
         <v>3299</v>
       </c>
@@ -47928,7 +48201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3296" t="s">
         <v>3300</v>
       </c>
@@ -47939,7 +48212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3297" t="s">
         <v>3301</v>
       </c>
@@ -47950,7 +48223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3298" t="s">
         <v>3302</v>
       </c>
@@ -47961,7 +48234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3299" t="s">
         <v>3303</v>
       </c>
@@ -47969,7 +48242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3300" t="s">
         <v>3304</v>
       </c>
@@ -47980,7 +48253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3301" t="s">
         <v>3305</v>
       </c>
@@ -47991,7 +48264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3302" t="s">
         <v>3306</v>
       </c>
@@ -47999,7 +48272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3303" t="s">
         <v>3307</v>
       </c>
@@ -48009,8 +48282,11 @@
       <c r="F3303">
         <v>1</v>
       </c>
-    </row>
-    <row r="3304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3303" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3304" t="s">
         <v>3308</v>
       </c>
@@ -48021,7 +48297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3305" t="s">
         <v>3309</v>
       </c>
@@ -48029,7 +48305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3306" t="s">
         <v>3310</v>
       </c>
@@ -48040,7 +48316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3307" t="s">
         <v>3311</v>
       </c>
@@ -48054,7 +48330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3308" t="s">
         <v>3312</v>
       </c>
@@ -48068,7 +48344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3309" t="s">
         <v>3313</v>
       </c>
@@ -48082,7 +48358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3310" t="s">
         <v>3314</v>
       </c>
@@ -48093,7 +48369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3311" t="s">
         <v>3315</v>
       </c>
@@ -48107,7 +48383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3312" t="s">
         <v>3316</v>
       </c>
@@ -49329,7 +49605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3425" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3425" t="s">
         <v>3429</v>
       </c>
@@ -49339,8 +49615,11 @@
       <c r="E3425">
         <v>1</v>
       </c>
-    </row>
-    <row r="3426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3425" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3426" t="s">
         <v>3430</v>
       </c>
@@ -49350,8 +49629,11 @@
       <c r="D3426">
         <v>1</v>
       </c>
-    </row>
-    <row r="3427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3426" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3427" t="s">
         <v>3431</v>
       </c>
@@ -49361,24 +49643,33 @@
       <c r="D3427">
         <v>1</v>
       </c>
-    </row>
-    <row r="3428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3427" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3428" t="s">
         <v>3432</v>
       </c>
       <c r="B3428">
         <v>38</v>
       </c>
-    </row>
-    <row r="3429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3428" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3429" t="s">
         <v>3433</v>
       </c>
       <c r="B3429">
         <v>12</v>
       </c>
-    </row>
-    <row r="3430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3429" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3430" t="s">
         <v>3434</v>
       </c>
@@ -49388,8 +49679,11 @@
       <c r="G3430">
         <v>1</v>
       </c>
-    </row>
-    <row r="3431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3430" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3431" t="s">
         <v>3435</v>
       </c>
@@ -49397,7 +49691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3432" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3432" t="s">
         <v>3436</v>
       </c>
@@ -49405,7 +49699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3433" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3433" t="s">
         <v>3437</v>
       </c>
@@ -49419,7 +49713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3434" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3434" t="s">
         <v>3438</v>
       </c>
@@ -49432,8 +49726,11 @@
       <c r="G3434">
         <v>1</v>
       </c>
-    </row>
-    <row r="3435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3434" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3435" t="s">
         <v>3439</v>
       </c>
@@ -49447,7 +49744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3436" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3436" t="s">
         <v>3440</v>
       </c>
@@ -49458,7 +49755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3437" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3437" t="s">
         <v>3441</v>
       </c>
@@ -49466,7 +49763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3438" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3438" t="s">
         <v>3442</v>
       </c>
@@ -49477,7 +49774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3439" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3439" t="s">
         <v>3443</v>
       </c>
@@ -49491,7 +49788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3440" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3440" t="s">
         <v>3444</v>
       </c>
